--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -920,13 +920,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
+        <v>100</v>
+      </c>
+      <c r="M15" s="15">
         <v>300</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>60</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
         <v>10</v>
       </c>
       <c r="K16" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.620689655172</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.650793650793</v>
+        <v>-93.665158371040</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-10</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
         <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>26.086956521739</v>
+        <v>20.833333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K17" s="15">
-        <v>6.25</v>
+        <v>10.810810810810</v>
       </c>
       <c r="L17" s="15">
-        <v>21.428571428571</v>
+        <v>32.258064516129</v>
       </c>
       <c r="M17" s="15">
-        <v>36</v>
+        <v>57.692307692307</v>
       </c>
       <c r="N17" s="15">
-        <v>-59.523809523809</v>
+        <v>-57.731958762886</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
         <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K18" s="15">
-        <v>28.571428571428</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="15">
         <v>28.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.048780487804</v>
+        <v>-82</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.120689655172</v>
+        <v>-96.511627906976</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
         <v>4</v>
       </c>
       <c r="E19" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F19" s="14">
+        <v>20</v>
+      </c>
+      <c r="G19" s="14">
+        <v>20</v>
+      </c>
+      <c r="H19" s="15">
         <v>0</v>
       </c>
-      <c r="F19" s="14">
-        <v>23</v>
-      </c>
-      <c r="G19" s="14">
-        <v>20</v>
-      </c>
-      <c r="H19" s="15">
-        <v>15</v>
-      </c>
       <c r="I19" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K19" s="15">
-        <v>10.714285714285</v>
+        <v>6.25</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.888888888888</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="M19" s="15">
-        <v>-38</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="N19" s="15">
-        <v>-18.421052631578</v>
+        <v>-22.727272727272</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
@@ -1116,22 +1116,22 @@
         <v>-44.444444444444</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>-27.272727272727</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M20" s="15">
-        <v>-63.636363636363</v>
+        <v>-64</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.263157894736</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>5.797101449275</v>
+        <v>1.492537313432</v>
       </c>
       <c r="I21" s="17">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J21" s="17">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="K21" s="18">
-        <v>6.521739130434</v>
+        <v>4.716981132075</v>
       </c>
       <c r="L21" s="18">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
-        <v>-41.317365269461</v>
+        <v>-40.641711229946</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.445366528354</v>
+        <v>-86.594202898550</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.428571428571</v>
+        <v>200</v>
       </c>
       <c r="F24" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G24" s="14">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="H24" s="15">
-        <v>-37.037037037037</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="I24" s="14">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="J24" s="14">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K24" s="15">
-        <v>-32.758620689655</v>
+        <v>-20.491803278688</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.415094339622</v>
+        <v>-20.491803278688</v>
       </c>
       <c r="M24" s="15">
-        <v>-29.729729729729</v>
+        <v>-21.774193548387</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>2</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="14">
         <v>16</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K25" s="15">
-        <v>-40.740740740740</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>-15.789473684210</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>48.484848484848</v>
+        <v>22.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="J26" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K26" s="15">
-        <v>47.826086956521</v>
+        <v>46.296296296296</v>
       </c>
       <c r="L26" s="15">
-        <v>33.333333333333</v>
+        <v>21.538461538461</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.449275362318</v>
+        <v>-5.952380952380</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1412,7 +1412,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="14">
-        <v>4</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-25</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
       <c r="H28" s="15">
-        <v>-28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
-      </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-50</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L31" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-61.538461538461</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>5</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>60</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K16" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.665158371040</v>
+        <v>-93.975903614457</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="F17" s="14">
+        <v>27</v>
+      </c>
+      <c r="G17" s="14">
+        <v>22</v>
+      </c>
+      <c r="H17" s="15">
+        <v>22.727272727272</v>
+      </c>
+      <c r="I17" s="14">
+        <v>49</v>
+      </c>
+      <c r="J17" s="14">
         <v>40</v>
       </c>
-      <c r="F17" s="14">
-        <v>29</v>
-      </c>
-      <c r="G17" s="14">
-        <v>24</v>
-      </c>
-      <c r="H17" s="15">
-        <v>20.833333333333</v>
-      </c>
-      <c r="I17" s="14">
-        <v>41</v>
-      </c>
-      <c r="J17" s="14">
-        <v>37</v>
-      </c>
       <c r="K17" s="15">
-        <v>10.810810810810</v>
+        <v>22.5</v>
       </c>
       <c r="L17" s="15">
-        <v>32.258064516129</v>
+        <v>40</v>
       </c>
       <c r="M17" s="15">
-        <v>57.692307692307</v>
+        <v>48.484848484848</v>
       </c>
       <c r="N17" s="15">
-        <v>-57.731958762886</v>
+        <v>-57.017543859649</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K18" s="15">
-        <v>-10</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>28.571428571428</v>
+        <v>37.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-82</v>
+        <v>-78.431372549019</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.511627906976</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
         <v>20</v>
@@ -1075,22 +1075,22 @@
         <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J19" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K19" s="15">
-        <v>6.25</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.444444444444</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M19" s="15">
-        <v>-38.181818181818</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-22.727272727272</v>
+        <v>-23.076923076923</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>-44.444444444444</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="15">
-        <v>-30.769230769230</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L20" s="15">
-        <v>-10</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M20" s="15">
-        <v>-64</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.263157894736</v>
+        <v>-94.196428571428</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.142857142857</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>1.492537313432</v>
+        <v>2.898550724637</v>
       </c>
       <c r="I21" s="17">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="J21" s="17">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="K21" s="18">
-        <v>4.716981132075</v>
+        <v>8.130081300813</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>9.917355371900</v>
       </c>
       <c r="M21" s="18">
-        <v>-40.641711229946</v>
+        <v>-36.057692307692</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.594202898550</v>
+        <v>-86.102403343782</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,29 +1223,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-100</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>21</v>
+      <c r="J23" s="14">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-100</v>
       </c>
       <c r="L23" s="15">
         <v>-100</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>200</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F24" s="14">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G24" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.677419354838</v>
+        <v>-23.880597014925</v>
       </c>
       <c r="I24" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J24" s="14">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="K24" s="15">
-        <v>-20.491803278688</v>
+        <v>-25.694444444444</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.491803278688</v>
+        <v>-21.897810218978</v>
       </c>
       <c r="M24" s="15">
-        <v>-21.774193548387</v>
+        <v>-22.463768115942</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
         <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I25" s="14">
         <v>16</v>
       </c>
       <c r="J25" s="14">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K25" s="15">
-        <v>-42.857142857142</v>
+        <v>-56.756756756756</v>
       </c>
       <c r="L25" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>25</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>22.857142857142</v>
+        <v>24.242424242424</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J26" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K26" s="15">
-        <v>46.296296296296</v>
+        <v>53.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>21.538461538461</v>
+        <v>31.428571428571</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.952380952380</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="L28" s="15">
-        <v>57.142857142857</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,13 +1558,13 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -914,16 +914,16 @@
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="N15" s="15">
         <v>-61.538461538461</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
         <v>9</v>
       </c>
-      <c r="G16" s="14">
-        <v>7</v>
-      </c>
       <c r="H16" s="15">
-        <v>28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
         <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-6.25</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.975903614457</v>
+        <v>-94.584837545126</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14">
         <v>7</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>133.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>22.727272727272</v>
+        <v>16</v>
       </c>
       <c r="I17" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J17" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K17" s="15">
-        <v>22.5</v>
+        <v>17.021276595744</v>
       </c>
       <c r="L17" s="15">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="M17" s="15">
-        <v>48.484848484848</v>
+        <v>37.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-57.017543859649</v>
+        <v>-55.284552845528</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.285714285714</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18" s="14">
         <v>12</v>
       </c>
       <c r="K18" s="15">
-        <v>-8.333333333333</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-78.431372549019</v>
+        <v>-77.586206896551</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.130952380952</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I19" s="14">
+        <v>44</v>
+      </c>
+      <c r="J19" s="14">
         <v>40</v>
       </c>
-      <c r="J19" s="14">
-        <v>38</v>
-      </c>
       <c r="K19" s="15">
-        <v>5.263157894736</v>
+        <v>10</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.043478260869</v>
+        <v>-12</v>
       </c>
       <c r="M19" s="15">
+        <v>-37.142857142857</v>
+      </c>
+      <c r="N19" s="15">
         <v>-33.333333333333</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-23.076923076923</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>-7.142857142857</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L20" s="15">
-        <v>18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-53.571428571428</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.196428571428</v>
+        <v>-94.190871369294</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>23.529411764705</v>
+        <v>-18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>2.898550724637</v>
+        <v>-4.411764705882</v>
       </c>
       <c r="I21" s="17">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J21" s="17">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="K21" s="18">
-        <v>8.130081300813</v>
+        <v>5.035971223021</v>
       </c>
       <c r="L21" s="18">
-        <v>9.917355371900</v>
+        <v>8.955223880597</v>
       </c>
       <c r="M21" s="18">
-        <v>-36.057692307692</v>
+        <v>-38.912133891213</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.102403343782</v>
+        <v>-86.278195488721</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1223,11 +1223,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-54.545454545454</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F24" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G24" s="14">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.880597014925</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="I24" s="14">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="J24" s="14">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.694444444444</v>
+        <v>-24.223602484472</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.897810218978</v>
+        <v>-22.784810126582</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.463768115942</v>
+        <v>-20.779220779220</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-83.333333333333</v>
+        <v>-77.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K25" s="15">
-        <v>-56.756756756756</v>
+        <v>-58.695652173913</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>116.666666666667</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="14">
         <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>24.242424242424</v>
+        <v>51.851851851851</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="J26" s="14">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K26" s="15">
-        <v>53.333333333333</v>
+        <v>56.060606060606</v>
       </c>
       <c r="L26" s="15">
-        <v>31.428571428571</v>
+        <v>21.176470588235</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.166666666666</v>
+        <v>-8.849557522123</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1406,13 +1406,13 @@
         <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>44.444444444444</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.444444444444</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.444444444444</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>2</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>5</v>
@@ -920,54 +920,54 @@
         <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
         <v>150</v>
       </c>
       <c r="N15" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.764705882352</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M16" s="15">
-        <v>-62.5</v>
+        <v>-62.790697674418</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.584837545126</v>
+        <v>-95.061728395061</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-14.285714285714</v>
+        <v>85.714285714285</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I17" s="14">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K17" s="15">
-        <v>17.021276595744</v>
+        <v>25.925925925925</v>
       </c>
       <c r="L17" s="15">
-        <v>37.5</v>
+        <v>61.904761904761</v>
       </c>
       <c r="M17" s="15">
-        <v>37.5</v>
+        <v>58.139534883720</v>
       </c>
       <c r="N17" s="15">
-        <v>-55.284552845528</v>
+        <v>-52.112676056338</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="15">
-        <v>8.333333333333</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>62.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.586206896551</v>
+        <v>-77.272727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.130952380952</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>6.25</v>
+        <v>-10</v>
       </c>
       <c r="I19" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J19" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K19" s="15">
-        <v>10</v>
+        <v>2.083333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-12</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="M19" s="15">
-        <v>-37.142857142857</v>
+        <v>-37.179487179487</v>
       </c>
       <c r="N19" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.974683544303</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
+        <v>8</v>
+      </c>
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="G20" s="14">
-        <v>11</v>
-      </c>
       <c r="H20" s="15">
-        <v>-45.454545454545</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J20" s="14">
         <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.647058823529</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L20" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M20" s="15">
-        <v>-51.724137931034</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.190871369294</v>
+        <v>-93.916349809885</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.75</v>
+        <v>27.777777777777</v>
       </c>
       <c r="F21" s="17">
+        <v>70</v>
+      </c>
+      <c r="G21" s="17">
         <v>65</v>
       </c>
-      <c r="G21" s="17">
-        <v>68</v>
-      </c>
       <c r="H21" s="18">
-        <v>-4.411764705882</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I21" s="17">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="J21" s="17">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K21" s="18">
-        <v>5.035971223021</v>
+        <v>7.643312101910</v>
       </c>
       <c r="L21" s="18">
-        <v>8.955223880597</v>
+        <v>17.361111111111</v>
       </c>
       <c r="M21" s="18">
-        <v>-38.912133891213</v>
+        <v>-35.984848484848</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.278195488721</v>
+        <v>-85.975103734439</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.647058823529</v>
+        <v>43.75</v>
       </c>
       <c r="F24" s="14">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G24" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.779661016949</v>
+        <v>8.196721311475</v>
       </c>
       <c r="I24" s="14">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="J24" s="14">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.223602484472</v>
+        <v>-18.079096045197</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.784810126582</v>
+        <v>-20.329670329670</v>
       </c>
       <c r="M24" s="15">
-        <v>-20.779220779220</v>
+        <v>-13.690476190476</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,10 +1303,10 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
         <v>-66.666666666666</v>
@@ -1315,22 +1315,22 @@
         <v>5</v>
       </c>
       <c r="G25" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-77.272727272727</v>
+        <v>-80</v>
       </c>
       <c r="I25" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J25" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K25" s="15">
-        <v>-58.695652173913</v>
+        <v>-59.615384615384</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.142857142857</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>83.333333333333</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>51.851851851851</v>
+        <v>55.172413793103</v>
       </c>
       <c r="I26" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J26" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K26" s="15">
-        <v>56.060606060606</v>
+        <v>48</v>
       </c>
       <c r="L26" s="15">
-        <v>21.176470588235</v>
+        <v>23.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.849557522123</v>
+        <v>-13.28125</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
@@ -1412,7 +1412,7 @@
         <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>175</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>36.363636363636</v>
+        <v>46.153846153846</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.473684210526</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.473684210526</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>-100</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
+        <v>6</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-64.285714285714</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-55.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
         <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.789473684210</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L16" s="15">
-        <v>-5.882352941176</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M16" s="15">
-        <v>-62.790697674418</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.061728395061</v>
+        <v>-94.350282485875</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>85.714285714285</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J17" s="14">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>25.925925925925</v>
+        <v>7.575757575757</v>
       </c>
       <c r="L17" s="15">
-        <v>61.904761904761</v>
+        <v>54.347826086956</v>
       </c>
       <c r="M17" s="15">
-        <v>58.139534883720</v>
+        <v>47.916666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.112676056338</v>
+        <v>-55.625</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.285714285714</v>
+        <v>40</v>
       </c>
       <c r="I18" s="14">
+        <v>16</v>
+      </c>
+      <c r="J18" s="14">
         <v>15</v>
       </c>
-      <c r="J18" s="14">
-        <v>14</v>
-      </c>
       <c r="K18" s="15">
-        <v>7.142857142857</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.272727272727</v>
+        <v>-77.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-96</v>
+        <v>-96.019900497512</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-37.5</v>
+        <v>300</v>
       </c>
       <c r="F19" s="14">
+        <v>24</v>
+      </c>
+      <c r="G19" s="14">
         <v>18</v>
       </c>
-      <c r="G19" s="14">
-        <v>20</v>
-      </c>
       <c r="H19" s="15">
-        <v>-10</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J19" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K19" s="15">
-        <v>2.083333333333</v>
+        <v>14</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.259259259259</v>
+        <v>-12.307692307692</v>
       </c>
       <c r="M19" s="15">
-        <v>-37.179487179487</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.974683544303</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.882352941176</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L20" s="15">
-        <v>14.285714285714</v>
+        <v>26.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-48.648648648648</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.916349809885</v>
+        <v>-93.238434163701</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>27.777777777777</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>7.692307692307</v>
+        <v>14.705882352941</v>
       </c>
       <c r="I21" s="17">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="J21" s="17">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="K21" s="18">
-        <v>7.643312101910</v>
+        <v>8.620689655172</v>
       </c>
       <c r="L21" s="18">
-        <v>17.361111111111</v>
+        <v>14.545454545454</v>
       </c>
       <c r="M21" s="18">
-        <v>-35.984848484848</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.975103734439</v>
+        <v>-85.638297872340</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1229,29 +1229,29 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="F23" s="14">
+        <v>1</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
+        <v>1</v>
       </c>
       <c r="J23" s="14">
         <v>1</v>
       </c>
       <c r="K23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>43.75</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F24" s="14">
         <v>66</v>
       </c>
       <c r="G24" s="14">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="H24" s="15">
-        <v>8.196721311475</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="I24" s="14">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J24" s="14">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.079096045197</v>
+        <v>-17.346938775510</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.329670329670</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.690476190476</v>
+        <v>-11.956521739130</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,32 +1305,32 @@
       <c r="C25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="14">
-        <v>6</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-66.666666666666</v>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H25" s="15">
-        <v>-80</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
         <v>52</v>
       </c>
       <c r="K25" s="15">
-        <v>-59.615384615384</v>
+        <v>-50</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.235294117647</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>11.111111111111</v>
+        <v>125</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
         <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>55.172413793103</v>
+        <v>86.206896551724</v>
       </c>
       <c r="I26" s="14">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="J26" s="14">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="K26" s="15">
-        <v>48</v>
+        <v>57.831325301204</v>
       </c>
       <c r="L26" s="15">
-        <v>23.333333333333</v>
+        <v>33.673469387755</v>
       </c>
       <c r="M26" s="15">
-        <v>-13.28125</v>
+        <v>-9.655172413793</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
         <v>5</v>
       </c>
-      <c r="J27" s="14">
-        <v>4</v>
-      </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>58.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>46.153846153846</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.476190476190</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,46 +869,46 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -920,10 +920,10 @@
         <v>20</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
         <v>-62.5</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>60</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>5.263157894736</v>
+        <v>15</v>
       </c>
       <c r="L16" s="15">
-        <v>5.263157894736</v>
+        <v>15</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.521739130434</v>
+        <v>-53.061224489795</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.350282485875</v>
+        <v>-93.850267379679</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K17" s="15">
-        <v>7.575757575757</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="15">
-        <v>54.347826086956</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>47.916666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>-55.625</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F18" s="14">
+        <v>6</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>7</v>
-      </c>
-      <c r="G18" s="14">
-        <v>5</v>
-      </c>
-      <c r="H18" s="15">
-        <v>40</v>
-      </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>6.666666666666</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>33.333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.142857142857</v>
+        <v>-76.712328767123</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.019900497512</v>
+        <v>-96.082949308755</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="I19" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J19" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K19" s="15">
-        <v>14</v>
+        <v>25.925925925925</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.307692307692</v>
+        <v>1.492537313432</v>
       </c>
       <c r="M19" s="15">
-        <v>-32.142857142857</v>
+        <v>-21.839080459770</v>
       </c>
       <c r="N19" s="15">
-        <v>-40</v>
+        <v>-37.037037037037</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I20" s="14">
         <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="15">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15">
         <v>5.555555555555</v>
       </c>
-      <c r="L20" s="15">
-        <v>26.666666666666</v>
-      </c>
       <c r="M20" s="15">
-        <v>-48.648648648648</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.238434163701</v>
+        <v>-93.537414965986</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>23.529411764705</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>14.705882352941</v>
+        <v>5.797101449275</v>
       </c>
       <c r="I21" s="17">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="J21" s="17">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="K21" s="18">
-        <v>8.620689655172</v>
+        <v>7.291666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>14.545454545454</v>
+        <v>11.956521739130</v>
       </c>
       <c r="M21" s="18">
-        <v>-34.146341463414</v>
+        <v>-32.679738562091</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.638297872340</v>
+        <v>-85.431400282885</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>200</v>
       </c>
       <c r="L22" s="15">
         <v>50</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>0</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>15</v>
+      </c>
+      <c r="D24" s="14">
         <v>16</v>
       </c>
-      <c r="D24" s="14">
-        <v>19</v>
-      </c>
       <c r="E24" s="15">
-        <v>-15.789473684210</v>
+        <v>-6.25</v>
       </c>
       <c r="F24" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.810810810810</v>
+        <v>2.941176470588</v>
       </c>
       <c r="I24" s="14">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="J24" s="14">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.346938775510</v>
+        <v>-16.509433962264</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.923076923076</v>
+        <v>-15.311004784689</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.956521739130</v>
+        <v>-15.311004784689</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>3</v>
+      </c>
+      <c r="D25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="E25" s="15">
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>-58.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J25" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K25" s="15">
-        <v>-50</v>
+        <v>-46.296296296296</v>
       </c>
       <c r="L25" s="15">
-        <v>-27.777777777777</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>125</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>86.206896551724</v>
+        <v>52.941176470588</v>
       </c>
       <c r="I26" s="14">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>57.831325301204</v>
+        <v>51.063829787234</v>
       </c>
       <c r="L26" s="15">
-        <v>33.673469387755</v>
+        <v>37.864077669902</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.655172413793</v>
+        <v>-12.883435582822</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
@@ -1412,7 +1412,7 @@
         <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>66.666666666666</v>
+        <v>61.538461538461</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.304347826087</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.909090909090</v>
+        <v>-92</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -881,8 +881,8 @@
       <c r="L14" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>0</v>
       </c>
       <c r="N14" s="15">
         <v>-87.5</v>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -914,60 +914,60 @@
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="I16" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>15</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>15</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.061224489795</v>
+        <v>-56.363636363636</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.850267379679</v>
+        <v>-93.893129770992</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-88.888888888888</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>-34.285714285714</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="I17" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J17" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K17" s="15">
-        <v>-4</v>
+        <v>-1.234567901234</v>
       </c>
       <c r="L17" s="15">
-        <v>33.333333333333</v>
+        <v>40.350877192982</v>
       </c>
       <c r="M17" s="15">
-        <v>28.571428571428</v>
+        <v>35.593220338983</v>
       </c>
       <c r="N17" s="15">
-        <v>-60</v>
+        <v>-58.549222797927</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="I18" s="14">
+        <v>19</v>
+      </c>
+      <c r="J18" s="14">
+        <v>19</v>
+      </c>
+      <c r="K18" s="15">
         <v>0</v>
       </c>
-      <c r="I18" s="14">
-        <v>17</v>
-      </c>
-      <c r="J18" s="14">
-        <v>18</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-5.555555555555</v>
-      </c>
       <c r="L18" s="15">
-        <v>6.25</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.712328767123</v>
+        <v>-76.543209876543</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.082949308755</v>
+        <v>-96.016771488469</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>75</v>
+        <v>38.095238095238</v>
       </c>
       <c r="I19" s="14">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J19" s="14">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="K19" s="15">
-        <v>25.925925925925</v>
+        <v>24.590163934426</v>
       </c>
       <c r="L19" s="15">
-        <v>1.492537313432</v>
+        <v>4.109589041095</v>
       </c>
       <c r="M19" s="15">
-        <v>-21.839080459770</v>
+        <v>-18.279569892473</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.037037037037</v>
+        <v>-36.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>20</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="15">
-        <v>5.555555555555</v>
+        <v>-5</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.537414965986</v>
+        <v>-94.242424242424</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1148,31 +1148,31 @@
         <v>-11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>5.797101449275</v>
+        <v>7.042253521126</v>
       </c>
       <c r="I21" s="17">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="J21" s="17">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="K21" s="18">
-        <v>7.291666666666</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L21" s="18">
-        <v>11.956521739130</v>
+        <v>14.213197969543</v>
       </c>
       <c r="M21" s="18">
-        <v>-32.679738562091</v>
+        <v>-32.228915662650</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.431400282885</v>
+        <v>-85.380116959064</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.25</v>
+        <v>122.222222222222</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H24" s="15">
-        <v>2.941176470588</v>
+        <v>23.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="J24" s="14">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.509433962264</v>
+        <v>-12.217194570135</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.311004784689</v>
+        <v>-14.159292035398</v>
       </c>
       <c r="M24" s="15">
-        <v>-15.311004784689</v>
+        <v>-13.004484304932</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>2</v>
-      </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.529411764705</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J25" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.296296296296</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.684210526315</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>52.941176470588</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K26" s="15">
-        <v>51.063829787234</v>
+        <v>46.078431372549</v>
       </c>
       <c r="L26" s="15">
-        <v>37.864077669902</v>
+        <v>30.701754385964</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.883435582822</v>
+        <v>-15.819209039548</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
+        <v>7</v>
+      </c>
+      <c r="J27" s="14">
         <v>6</v>
       </c>
-      <c r="J27" s="14">
-        <v>5</v>
-      </c>
       <c r="K27" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I28" s="14">
         <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>61.538461538461</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>31.25</v>
+        <v>23.529411764705</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.307692307692</v>
+        <v>-92.592592592592</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-92</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
+        <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,55 +892,55 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>9</v>
@@ -952,22 +952,22 @@
         <v>125</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>9.090909090909</v>
+        <v>13.043478260869</v>
       </c>
       <c r="L16" s="15">
-        <v>14.285714285714</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.363636363636</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.893129770992</v>
+        <v>-94.157303370786</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,63 +975,63 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>16.666666666666</v>
+        <v>10</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.470588235294</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="I17" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.234567901234</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>40.350877192982</v>
+        <v>35.820895522388</v>
       </c>
       <c r="M17" s="15">
-        <v>35.593220338983</v>
+        <v>49.180327868852</v>
       </c>
       <c r="N17" s="15">
-        <v>-58.549222797927</v>
+        <v>-57.276995305164</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>100</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-14.285714285714</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
         <v>19</v>
@@ -1043,13 +1043,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>11.764705882352</v>
+        <v>-5</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.543209876543</v>
+        <v>-77.647058823529</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.016771488469</v>
+        <v>-96.281800391389</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>38.095238095238</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I19" s="14">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>24.590163934426</v>
+        <v>22.857142857142</v>
       </c>
       <c r="L19" s="15">
-        <v>4.109589041095</v>
+        <v>10.256410256410</v>
       </c>
       <c r="M19" s="15">
-        <v>-18.279569892473</v>
+        <v>-11.340206185567</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.666666666666</v>
+        <v>-36.296296296296</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="C20" s="14">
+        <v>3</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" s="14">
         <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="L20" s="15">
-        <v>-5</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M20" s="15">
-        <v>-51.282051282051</v>
+        <v>-45</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.242424242424</v>
+        <v>-93.802816901408</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>7.042253521126</v>
+        <v>9.459459459459</v>
       </c>
       <c r="I21" s="17">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="J21" s="17">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="K21" s="18">
-        <v>7.142857142857</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L21" s="18">
-        <v>14.213197969543</v>
+        <v>15</v>
       </c>
       <c r="M21" s="18">
-        <v>-32.228915662650</v>
+        <v>-27.714285714285</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.380116959064</v>
+        <v>-85.002963841138</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,10 +1207,10 @@
         <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-70</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>122.222222222222</v>
+        <v>-35</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G24" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H24" s="15">
-        <v>23.333333333333</v>
+        <v>-1.5625</v>
       </c>
       <c r="I24" s="14">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J24" s="14">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.217194570135</v>
+        <v>-14.107883817427</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.159292035398</v>
+        <v>-12.288135593220</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.004484304932</v>
+        <v>-13.025210084033</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
         <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I25" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J25" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.368421052631</v>
+        <v>-49.206349206349</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.571428571428</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>15</v>
       </c>
       <c r="I26" s="14">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="J26" s="14">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="K26" s="15">
-        <v>46.078431372549</v>
+        <v>38.260869565217</v>
       </c>
       <c r="L26" s="15">
-        <v>30.701754385964</v>
+        <v>22.307692307692</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.819209039548</v>
+        <v>-14.973262032085</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="14">
+        <v>12</v>
+      </c>
+      <c r="J27" s="14">
         <v>7</v>
       </c>
-      <c r="J27" s="14">
-        <v>6</v>
-      </c>
       <c r="K27" s="15">
-        <v>16.666666666666</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="L28" s="15">
-        <v>23.529411764705</v>
+        <v>35.294117647058</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.592592592592</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1561,19 +1561,19 @@
         <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L31" s="15">
         <v>100</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -879,13 +879,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L15" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>125</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>13.043478260869</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L16" s="15">
-        <v>8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.064516129032</v>
+        <v>-59.420289855072</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.157303370786</v>
+        <v>-94.178794178794</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>10</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.135135135135</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="15">
-        <v>35.820895522388</v>
+        <v>40.277777777777</v>
       </c>
       <c r="M17" s="15">
-        <v>49.180327868852</v>
+        <v>40.277777777777</v>
       </c>
       <c r="N17" s="15">
-        <v>-57.276995305164</v>
+        <v>-56.465517241379</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L18" s="15">
-        <v>-5</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.647058823529</v>
+        <v>-75.581395348837</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.281800391389</v>
+        <v>-96.236559139784</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>54.545454545454</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I19" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K19" s="15">
-        <v>22.857142857142</v>
+        <v>22.077922077922</v>
       </c>
       <c r="L19" s="15">
-        <v>10.256410256410</v>
+        <v>17.5</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.340206185567</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="N19" s="15">
-        <v>-36.296296296296</v>
+        <v>-38.562091503268</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>10</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L20" s="15">
-        <v>4.761904761904</v>
+        <v>9.523809523809</v>
       </c>
       <c r="M20" s="15">
-        <v>-45</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.802816901408</v>
+        <v>-93.850267379679</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>9.459459459459</v>
+        <v>3.797468354430</v>
       </c>
       <c r="I21" s="17">
+        <v>277</v>
+      </c>
+      <c r="J21" s="17">
         <v>253</v>
       </c>
-      <c r="J21" s="17">
-        <v>231</v>
-      </c>
       <c r="K21" s="18">
-        <v>9.523809523809</v>
+        <v>9.486166007905</v>
       </c>
       <c r="L21" s="18">
-        <v>15</v>
+        <v>18.884120171673</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.714285714285</v>
+        <v>-26.912928759894</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.002963841138</v>
+        <v>-84.838533114395</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-70</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1229,8 +1229,8 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
         <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-35</v>
+        <v>5</v>
       </c>
       <c r="F24" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.5625</v>
+        <v>4.615384615384</v>
       </c>
       <c r="I24" s="14">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="J24" s="14">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.107883817427</v>
+        <v>-12.643678160919</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.288135593220</v>
+        <v>-11.284046692607</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.025210084033</v>
+        <v>-10.9375</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
         <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.272727272727</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J25" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K25" s="15">
-        <v>-49.206349206349</v>
+        <v>-50</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.581395348837</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-23.076923076923</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>15</v>
+        <v>2.439024390243</v>
       </c>
       <c r="I26" s="14">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>38.260869565217</v>
+        <v>37.903225806451</v>
       </c>
       <c r="L26" s="15">
-        <v>22.307692307692</v>
+        <v>24.817518248175</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.973262032085</v>
+        <v>-19.339622641509</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>5</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>133.333333333333</v>
+        <v>250</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>71.428571428571</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L27" s="15">
-        <v>71.428571428571</v>
+        <v>30</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F28" s="14">
+        <v>8</v>
+      </c>
+      <c r="G28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>43.75</v>
+        <v>64.705882352941</v>
       </c>
       <c r="L28" s="15">
-        <v>35.294117647058</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.548387096774</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.333333333333</v>
+        <v>-93.939393939393</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1561,22 +1561,22 @@
         <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K31" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -870,30 +870,30 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-88.888888888888</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,48 +926,48 @@
         <v>125</v>
       </c>
       <c r="N15" s="15">
-        <v>-55</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
+        <v>8</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>4</v>
       </c>
-      <c r="E16" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F16" s="14">
-        <v>7</v>
-      </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="I16" s="14">
         <v>28</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>3.703703703703</v>
+        <v>-20</v>
       </c>
       <c r="L16" s="15">
         <v>16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-59.420289855072</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.178794178794</v>
+        <v>-94.563106796116</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>11.111111111111</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.705882352941</v>
+        <v>6.25</v>
       </c>
       <c r="I17" s="14">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J17" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K17" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>40.277777777777</v>
+        <v>38.961038961039</v>
       </c>
       <c r="M17" s="15">
-        <v>40.277777777777</v>
+        <v>38.961038961039</v>
       </c>
       <c r="N17" s="15">
-        <v>-56.465517241379</v>
+        <v>-58.687258687258</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>5</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.5</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-75.581395348837</v>
+        <v>-73.863636363636</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.236559139784</v>
+        <v>-96.088435374149</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
+        <v>30</v>
+      </c>
+      <c r="G19" s="14">
         <v>33</v>
       </c>
-      <c r="G19" s="14">
-        <v>27</v>
-      </c>
       <c r="H19" s="15">
-        <v>22.222222222222</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K19" s="15">
-        <v>22.077922077922</v>
+        <v>14.942528735632</v>
       </c>
       <c r="L19" s="15">
-        <v>17.5</v>
+        <v>16.279069767441</v>
       </c>
       <c r="M19" s="15">
-        <v>-11.320754716981</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.562091503268</v>
+        <v>-38.650306748466</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
+        <v>5</v>
+      </c>
+      <c r="G20" s="14">
         <v>4</v>
       </c>
-      <c r="G20" s="14">
-        <v>3</v>
-      </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
+        <v>24</v>
+      </c>
+      <c r="J20" s="14">
         <v>23</v>
       </c>
-      <c r="J20" s="14">
-        <v>21</v>
-      </c>
       <c r="K20" s="15">
-        <v>9.523809523809</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L20" s="15">
-        <v>9.523809523809</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M20" s="15">
-        <v>-43.902439024390</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.850267379679</v>
+        <v>-94.103194103194</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>4.545454545454</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>3.797468354430</v>
+        <v>-6.741573033707</v>
       </c>
       <c r="I21" s="17">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="J21" s="17">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="K21" s="18">
-        <v>9.486166007905</v>
+        <v>4.270462633451</v>
       </c>
       <c r="L21" s="18">
-        <v>18.884120171673</v>
+        <v>19.591836734693</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.912928759894</v>
+        <v>-27.114427860696</v>
       </c>
       <c r="N21" s="18">
-        <v>-84.838533114395</v>
+        <v>-85.073866530820</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
         <v>65</v>
       </c>
       <c r="H24" s="15">
-        <v>4.615384615384</v>
+        <v>10.769230769230</v>
       </c>
       <c r="I24" s="14">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="J24" s="14">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.643678160919</v>
+        <v>-11.191335740072</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.284046692607</v>
+        <v>-12.142857142857</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.9375</v>
+        <v>-9.890109890109</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="I25" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="K25" s="15">
         <v>-50</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.086956521739</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F26" s="14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>2.439024390243</v>
+        <v>8.571428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K26" s="15">
-        <v>37.903225806451</v>
+        <v>38.759689922480</v>
       </c>
       <c r="L26" s="15">
-        <v>24.817518248175</v>
+        <v>23.448275862069</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.339622641509</v>
+        <v>-21.145374449339</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>64.705882352941</v>
+        <v>57.894736842105</v>
       </c>
       <c r="L28" s="15">
-        <v>33.333333333333</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.939393939393</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3</v>
+      </c>
+      <c r="H31" s="15">
         <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14">
-        <v>4</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -905,10 +905,10 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -926,48 +926,48 @@
         <v>125</v>
       </c>
       <c r="N15" s="15">
-        <v>-57.142857142857</v>
+        <v>-60.869565217391</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>4</v>
       </c>
       <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F16" s="14">
         <v>8</v>
       </c>
-      <c r="E16" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="14">
-        <v>4</v>
-      </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-73.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
+        <v>32</v>
+      </c>
+      <c r="J16" s="14">
+        <v>38</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-15.789473684210</v>
+      </c>
+      <c r="L16" s="15">
         <v>28</v>
       </c>
-      <c r="J16" s="14">
-        <v>35</v>
-      </c>
-      <c r="K16" s="15">
-        <v>-20</v>
-      </c>
-      <c r="L16" s="15">
-        <v>16.666666666666</v>
-      </c>
       <c r="M16" s="15">
-        <v>-61.111111111111</v>
+        <v>-60</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.563106796116</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>7</v>
-      </c>
       <c r="E17" s="15">
-        <v>-14.285714285714</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
         <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="I17" s="14">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J17" s="14">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-2.654867256637</v>
       </c>
       <c r="L17" s="15">
-        <v>38.961038961039</v>
+        <v>39.240506329113</v>
       </c>
       <c r="M17" s="15">
-        <v>38.961038961039</v>
+        <v>34.146341463414</v>
       </c>
       <c r="N17" s="15">
-        <v>-58.687258687258</v>
+        <v>-61.538461538461</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>9.523809523809</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>-4.166666666666</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-73.863636363636</v>
+        <v>-72.340425531914</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.088435374149</v>
+        <v>-95.826645264847</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" s="14">
         <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.090909090909</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I19" s="14">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J19" s="14">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K19" s="15">
-        <v>14.942528735632</v>
+        <v>10.638297872340</v>
       </c>
       <c r="L19" s="15">
-        <v>16.279069767441</v>
+        <v>20.930232558139</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.043478260869</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.650306748466</v>
+        <v>-40.229885057471</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="I20" s="14">
+        <v>26</v>
+      </c>
+      <c r="J20" s="14">
         <v>24</v>
       </c>
-      <c r="J20" s="14">
-        <v>23</v>
-      </c>
       <c r="K20" s="15">
-        <v>4.347826086956</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>9.090909090909</v>
+        <v>13.043478260869</v>
       </c>
       <c r="M20" s="15">
-        <v>-46.666666666666</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.103194103194</v>
+        <v>-94.009216589861</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,13 +1139,13 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-42.857142857142</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
         <v>83</v>
@@ -1157,22 +1157,22 @@
         <v>-6.741573033707</v>
       </c>
       <c r="I21" s="17">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="J21" s="17">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="K21" s="18">
-        <v>4.270462633451</v>
+        <v>3.344481605351</v>
       </c>
       <c r="L21" s="18">
-        <v>19.591836734693</v>
+        <v>24.096385542168</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.114427860696</v>
+        <v>-28.139534883720</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.073866530820</v>
+        <v>-85.257633587786</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H24" s="15">
-        <v>10.769230769230</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="J24" s="14">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.191335740072</v>
+        <v>-9.246575342465</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.142857142857</v>
+        <v>-12.251655629139</v>
       </c>
       <c r="M24" s="15">
-        <v>-9.890109890109</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-59.090909090909</v>
+        <v>-60</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J25" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K25" s="15">
-        <v>-50</v>
+        <v>-51.219512195122</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.148936170212</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>44</v>
+      </c>
+      <c r="G26" s="14">
         <v>40</v>
       </c>
-      <c r="F26" s="14">
-        <v>38</v>
-      </c>
-      <c r="G26" s="14">
-        <v>35</v>
-      </c>
       <c r="H26" s="15">
-        <v>8.571428571428</v>
+        <v>10</v>
       </c>
       <c r="I26" s="14">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="J26" s="14">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="K26" s="15">
-        <v>38.759689922480</v>
+        <v>35.915492957746</v>
       </c>
       <c r="L26" s="15">
-        <v>23.448275862069</v>
+        <v>19.875776397515</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.145374449339</v>
+        <v>-21.224489795918</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K28" s="15">
-        <v>57.894736842105</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>36.363636363636</v>
+        <v>37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.285714285714</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.871794871794</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1570,10 +1570,10 @@
         <v>4</v>
       </c>
       <c r="J31" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L31" s="15">
         <v>33.333333333333</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="H15" s="15">
-        <v>200</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -920,13 +920,13 @@
         <v>28.571428571428</v>
       </c>
       <c r="L15" s="15">
-        <v>12.5</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M15" s="15">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-60.869565217391</v>
+        <v>-67.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.789473684210</v>
+        <v>-17.5</v>
       </c>
       <c r="L16" s="15">
-        <v>28</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M16" s="15">
-        <v>-60</v>
+        <v>-63.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.240837696335</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-6.25</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="I17" s="14">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J17" s="14">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.654867256637</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>39.240506329113</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>34.146341463414</v>
+        <v>25.842696629213</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.538461538461</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>133.333333333333</v>
+        <v>40</v>
       </c>
       <c r="I18" s="14">
         <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>8.333333333333</v>
+        <v>4</v>
       </c>
       <c r="M18" s="15">
-        <v>-72.340425531914</v>
+        <v>-74</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.826645264847</v>
+        <v>-96.006144393241</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-42.857142857142</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
         <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.181818181818</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I19" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J19" s="14">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K19" s="15">
-        <v>10.638297872340</v>
+        <v>9.708737864077</v>
       </c>
       <c r="L19" s="15">
-        <v>20.930232558139</v>
+        <v>26.966292134831</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.333333333333</v>
+        <v>-13.740458015267</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.229885057471</v>
+        <v>-38.251366120218</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>8.333333333333</v>
+        <v>8</v>
       </c>
       <c r="L20" s="15">
-        <v>13.043478260869</v>
+        <v>12.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-46.938775510204</v>
+        <v>-48.076923076923</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.009216589861</v>
+        <v>-94.091903719912</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
         <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.741573033707</v>
+        <v>-26.966292134831</v>
       </c>
       <c r="I21" s="17">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="J21" s="17">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="K21" s="18">
-        <v>3.344481605351</v>
+        <v>0.625</v>
       </c>
       <c r="L21" s="18">
-        <v>24.096385542168</v>
+        <v>21.969696969697</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.139534883720</v>
+        <v>-31.196581196581</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.257633587786</v>
+        <v>-85.449615906009</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="J24" s="14">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.246575342465</v>
+        <v>-8.306709265175</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.251655629139</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.169491525423</v>
+        <v>-8.598726114649</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,16 +1321,16 @@
         <v>-60</v>
       </c>
       <c r="I25" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J25" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K25" s="15">
-        <v>-51.219512195122</v>
+        <v>-52.272727272727</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.076923076923</v>
+        <v>-23.636363636363</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,13 +1344,13 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
         <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F26" s="14">
         <v>44</v>
@@ -1362,19 +1362,19 @@
         <v>10</v>
       </c>
       <c r="I26" s="14">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="J26" s="14">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="K26" s="15">
-        <v>35.915492957746</v>
+        <v>31.612903225806</v>
       </c>
       <c r="L26" s="15">
-        <v>19.875776397515</v>
+        <v>20</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.224489795918</v>
+        <v>-21.235521235521</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
-      </c>
-      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="H27" s="15">
-        <v>500</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
@@ -1412,7 +1412,7 @@
         <v>85.714285714285</v>
       </c>
       <c r="L27" s="15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>4</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>116.666666666667</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>33</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>37.5</v>
+        <v>32</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-95</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.871794871794</v>
+        <v>-95.555555555555</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-071pct.xlsx
+++ b/data/source/weekly/cs-en-us-071pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-67.857142857142</v>
+        <v>-68.965517241379</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-58.823529411764</v>
+        <v>-43.75</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>-17.5</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="L16" s="15">
-        <v>22.222222222222</v>
+        <v>23.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.333333333333</v>
+        <v>-62.626262626262</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.240837696335</v>
+        <v>-93.904448105436</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-71.428571428571</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
         <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-31.034482758620</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="I17" s="14">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J17" s="14">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.666666666666</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L17" s="15">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="M17" s="15">
-        <v>25.842696629213</v>
+        <v>27.173913043478</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.636363636363</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
         <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M18" s="15">
-        <v>-74</v>
+        <v>-73.584905660377</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.006144393241</v>
+        <v>-95.906432748538</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-27.272727272727</v>
+        <v>-37.5</v>
       </c>
       <c r="I19" s="14">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J19" s="14">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K19" s="15">
-        <v>9.708737864077</v>
+        <v>6.422018348623</v>
       </c>
       <c r="L19" s="15">
-        <v>26.966292134831</v>
+        <v>26.086956521739</v>
       </c>
       <c r="M19" s="15">
-        <v>-13.740458015267</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.251366120218</v>
+        <v>-42.288557213930</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="14">
         <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
+        <v>-3.571428571428</v>
+      </c>
+      <c r="L20" s="15">
         <v>8</v>
       </c>
-      <c r="L20" s="15">
-        <v>12.5</v>
-      </c>
       <c r="M20" s="15">
-        <v>-48.076923076923</v>
+        <v>-49.056603773584</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.091903719912</v>
+        <v>-94.351464435146</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
         <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-47.619047619047</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.966292134831</v>
+        <v>-35.227272727272</v>
       </c>
       <c r="I21" s="17">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="J21" s="17">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="K21" s="18">
-        <v>0.625</v>
+        <v>-1.466275659824</v>
       </c>
       <c r="L21" s="18">
-        <v>21.969696969697</v>
+        <v>21.299638989169</v>
       </c>
       <c r="M21" s="18">
-        <v>-31.196581196581</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.449615906009</v>
+        <v>-85.622593068035</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>4.761904761904</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H24" s="15">
-        <v>11.111111111111</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I24" s="14">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="J24" s="14">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.306709265175</v>
+        <v>-8.459214501510</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.888888888888</v>
+        <v>-9.009009009009</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.598726114649</v>
+        <v>-7.902735562310</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="14">
         <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H25" s="15">
-        <v>-60</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="I25" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J25" s="14">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.272727272727</v>
+        <v>-53.684210526315</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.636363636363</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>366.666666666667</v>
       </c>
       <c r="F26" s="14">
         <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>10</v>
+        <v>29.411764705882</v>
       </c>
       <c r="I26" s="14">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="J26" s="14">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K26" s="15">
-        <v>31.612903225806</v>
+        <v>37.341772151898</v>
       </c>
       <c r="L26" s="15">
-        <v>20</v>
+        <v>19.230769230769</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.235521235521</v>
+        <v>-21.376811594202</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>83.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K28" s="15">
         <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>32</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,32 +1469,32 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
         <v>-83.333333333333</v>
@@ -1510,32 +1510,32 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M30" s="15">
         <v>-77.777777777777</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
